--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -67,6 +70,12 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
     <t>B1628TM</t>
   </si>
   <si>
@@ -91,16 +100,37 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>19:28</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>15:01</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>19:28:00</t>
+  </si>
+  <si>
+    <t>10:54:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>15:01:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>3231391612 3231391612</t>
+  </si>
+  <si>
+    <t>3231611180 3231611180</t>
+  </si>
+  <si>
+    <t>3231723444 3231723444</t>
+  </si>
+  <si>
+    <t>3231894752 3231894752</t>
+  </si>
+  <si>
+    <t>3232518007 3232518007</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ</t>
@@ -524,24 +554,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -581,262 +613,321 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1146</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2">
         <v>67.28</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
         <v>1.67</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>112.36</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>121.1</v>
       </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>29</v>
       </c>
       <c r="M2">
-        <v>42487</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>116000</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1146</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>46.96</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>77.95</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.79</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>84.06</v>
       </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>128877</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1146</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>13.66</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
         <v>1.47</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>20.08</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>21.04</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>129964</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1146</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
       </c>
       <c r="F5">
         <v>47.68</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
         <v>1.49</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>71.04000000000001</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.54</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>73.43000000000001</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>34.2</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="L5">
+      <c r="H6">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="1">
+        <v>51.3</v>
+      </c>
+      <c r="J6">
+        <v>1.57</v>
+      </c>
+      <c r="K6" s="1">
+        <v>53.69</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>131515</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="6">
         <v>114.24</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.6659</v>
-      </c>
-      <c r="E10" s="6">
-        <v>190.31</v>
-      </c>
-      <c r="F10" s="6">
-        <v>205.16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="6">
-        <v>61.34</v>
       </c>
       <c r="C11" s="6">
         <v>2</v>
       </c>
       <c r="D11" s="7">
-        <v>1.4855</v>
+        <v>1.6659</v>
       </c>
       <c r="E11" s="6">
-        <v>91.12</v>
+        <v>190.31</v>
       </c>
       <c r="F11" s="6">
-        <v>94.47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="9">
-        <v>175.58</v>
-      </c>
-      <c r="C12" s="9">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>281.43</v>
-      </c>
-      <c r="F12" s="9">
-        <v>299.63</v>
+        <v>205.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="6">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1.4907</v>
+      </c>
+      <c r="E12" s="6">
+        <v>142.42</v>
+      </c>
+      <c r="F12" s="6">
+        <v>148.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="9">
+        <v>209.78</v>
+      </c>
+      <c r="C13" s="9">
+        <v>5</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9">
+        <v>332.73</v>
+      </c>
+      <c r="F13" s="9">
+        <v>353.32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -184,7 +184,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,12 +194,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,17 +243,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,48 +46,42 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Пирдоп</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>B3211HA</t>
   </si>
   <si>
     <t>B1628TM</t>
   </si>
   <si>
-    <t>B3211HA</t>
-  </si>
-  <si>
     <t>B1648HH</t>
   </si>
   <si>
+    <t>78970151027720088</t>
+  </si>
+  <si>
     <t>78970151027720062</t>
   </si>
   <si>
-    <t>78970151027720088</t>
-  </si>
-  <si>
     <t>78970151027720070</t>
   </si>
   <si>
@@ -98,39 +89,6 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>19:28:00</t>
-  </si>
-  <si>
-    <t>10:54:00</t>
-  </si>
-  <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>15:01:00</t>
-  </si>
-  <si>
-    <t>11:40:00</t>
-  </si>
-  <si>
-    <t>3231391612 3231391612</t>
-  </si>
-  <si>
-    <t>3231611180 3231611180</t>
-  </si>
-  <si>
-    <t>3231723444 3231723444</t>
-  </si>
-  <si>
-    <t>3231894752 3231894752</t>
-  </si>
-  <si>
-    <t>3232518007 3232518007</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ</t>
@@ -548,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -557,17 +515,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -601,327 +556,203 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>50.92</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="H2">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J2">
+        <v>86.05</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>58.19</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="H3">
+        <v>94.27</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J3">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>45.26</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H4">
+        <v>68.8</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J4">
+        <v>70.61</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2">
-        <v>67.28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2">
-        <v>1.67</v>
-      </c>
-      <c r="I2" s="1">
-        <v>112.36</v>
-      </c>
-      <c r="J2">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>121.1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2">
-        <v>116000</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B9" s="6">
+        <v>109.11</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.62</v>
+      </c>
+      <c r="E9" s="6">
+        <v>176.76</v>
+      </c>
+      <c r="F9" s="6">
+        <v>182.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>46.96</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3">
-        <v>1.66</v>
-      </c>
-      <c r="I3" s="1">
-        <v>77.95</v>
-      </c>
-      <c r="J3">
-        <v>1.79</v>
-      </c>
-      <c r="K3" s="1">
-        <v>84.06</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="B10" s="6">
+        <v>45.26</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.5201</v>
+      </c>
+      <c r="E10" s="6">
+        <v>68.8</v>
+      </c>
+      <c r="F10" s="6">
+        <v>70.61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>13.66</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4">
-        <v>1.47</v>
-      </c>
-      <c r="I4" s="1">
-        <v>20.08</v>
-      </c>
-      <c r="J4">
-        <v>1.54</v>
-      </c>
-      <c r="K4" s="1">
-        <v>21.04</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>47.68</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5">
-        <v>1.49</v>
-      </c>
-      <c r="I5" s="1">
-        <v>71.04000000000001</v>
-      </c>
-      <c r="J5">
-        <v>1.54</v>
-      </c>
-      <c r="K5" s="1">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6">
-        <v>34.2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6">
-        <v>1.5</v>
-      </c>
-      <c r="I6" s="1">
-        <v>51.3</v>
-      </c>
-      <c r="J6">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>53.69</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="6">
-        <v>114.24</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.6659</v>
-      </c>
-      <c r="E11" s="6">
-        <v>190.31</v>
-      </c>
-      <c r="F11" s="6">
-        <v>205.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="6">
-        <v>95.54000000000001</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="B11" s="9">
+        <v>154.37</v>
+      </c>
+      <c r="C11" s="9">
         <v>3</v>
       </c>
-      <c r="D12" s="7">
-        <v>1.4907</v>
-      </c>
-      <c r="E12" s="6">
-        <v>142.42</v>
-      </c>
-      <c r="F12" s="6">
-        <v>148.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="9">
-        <v>209.78</v>
-      </c>
-      <c r="C13" s="9">
-        <v>5</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>332.73</v>
-      </c>
-      <c r="F13" s="9">
-        <v>353.32</v>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9">
+        <v>245.56</v>
+      </c>
+      <c r="F11" s="9">
+        <v>253.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -64,13 +73,13 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Пирдоп</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1927 Пирдоп</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>B3211HA</t>
@@ -97,19 +106,37 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-01 16:17:45</t>
-  </si>
-  <si>
-    <t>2026-06-05 11:00:22</t>
-  </si>
-  <si>
-    <t>2026-06-10 11:18:03</t>
-  </si>
-  <si>
-    <t>2026-06-21 06:52:17</t>
-  </si>
-  <si>
-    <t>2026-06-24 16:17:54</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:17:00</t>
+  </si>
+  <si>
+    <t>10:57:00</t>
+  </si>
+  <si>
+    <t>11:17:00</t>
+  </si>
+  <si>
+    <t>06:52:00</t>
+  </si>
+  <si>
+    <t>16:18:00</t>
+  </si>
+  <si>
+    <t>3232717245 3232717245</t>
+  </si>
+  <si>
+    <t>3232913041 3232913041</t>
+  </si>
+  <si>
+    <t>3233124502 3233124502</t>
+  </si>
+  <si>
+    <t>3233607079 3233607079</t>
+  </si>
+  <si>
+    <t>3233811726 3233811726</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ</t>
@@ -527,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -536,14 +563,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,185 +607,239 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>50.92</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2">
         <v>1.62</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>82.48999999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>86.05</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>58.19</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
         <v>1.59</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>92.52</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>96.59999999999999</v>
       </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>45.26</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
         <v>1.48</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>66.98</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>70.61</v>
       </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>64.94</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5">
         <v>1.51</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>98.06</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.54</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>100.01</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>48.63</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
         <v>1.42</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>69.05</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.51</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>73.43000000000001</v>
       </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -763,29 +847,29 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6">
         <v>174.05</v>
@@ -803,9 +887,9 @@
         <v>282.66</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6">
         <v>93.89</v>
@@ -823,9 +907,9 @@
         <v>144.04</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:14">
       <c r="A13" s="8" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B13" s="9">
         <v>267.94</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-05</t>
   </si>
   <si>
@@ -64,10 +70,28 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1197 Разград</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
   </si>
   <si>
     <t>B1628TM</t>
@@ -94,16 +118,55 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-05 18:17:46</t>
-  </si>
-  <si>
-    <t>2026-07-07 12:59:39</t>
-  </si>
-  <si>
-    <t>2026-07-08 11:12:05</t>
-  </si>
-  <si>
-    <t>2026-07-15 13:13:23</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:19:00</t>
+  </si>
+  <si>
+    <t>12:59:00</t>
+  </si>
+  <si>
+    <t>11:12:00</t>
+  </si>
+  <si>
+    <t>13:13:00</t>
+  </si>
+  <si>
+    <t>10:39:00</t>
+  </si>
+  <si>
+    <t>07:56:00</t>
+  </si>
+  <si>
+    <t>12:48:00</t>
+  </si>
+  <si>
+    <t>14:55:00</t>
+  </si>
+  <si>
+    <t>3234358901 3234358901</t>
+  </si>
+  <si>
+    <t>3234437398 3234437398</t>
+  </si>
+  <si>
+    <t>3234470226 3234470226</t>
+  </si>
+  <si>
+    <t>3234806498 3234806498</t>
+  </si>
+  <si>
+    <t>3235041064 3235041064</t>
+  </si>
+  <si>
+    <t>3235352085 3235352085</t>
+  </si>
+  <si>
+    <t>3235526048 3235526048</t>
+  </si>
+  <si>
+    <t>3235585545 3235585545</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ</t>
@@ -521,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,15 +593,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -575,250 +640,456 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>64.28</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2">
         <v>1.45</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>93.20999999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>97.70999999999999</v>
       </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2">
         <v>123000</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>35.97</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3">
         <v>1.4</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>50.36</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.5</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>53.96</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>49.38</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4">
         <v>1.45</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>71.59999999999999</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.52</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>75.06</v>
       </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>16.11</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5">
         <v>1.41</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>22.72</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.49</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>24</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>46.35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6">
+        <v>1.57</v>
+      </c>
+      <c r="I6" s="1">
+        <v>72.77</v>
+      </c>
+      <c r="J6">
+        <v>1.68</v>
+      </c>
+      <c r="K6" s="1">
+        <v>77.87</v>
+      </c>
+      <c r="L6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="L5">
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>58</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>1.66</v>
+      </c>
+      <c r="I7" s="1">
+        <v>96.28</v>
+      </c>
+      <c r="J7">
+        <v>1.74</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100.92</v>
+      </c>
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>126000</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>33.13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8">
+        <v>1.49</v>
+      </c>
+      <c r="I8" s="1">
+        <v>49.36</v>
+      </c>
+      <c r="J8">
+        <v>1.55</v>
+      </c>
+      <c r="K8" s="1">
+        <v>51.35</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="N8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="F9">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>1.71</v>
+      </c>
+      <c r="I9" s="1">
+        <v>100.89</v>
+      </c>
+      <c r="J9">
+        <v>1.79</v>
+      </c>
+      <c r="K9" s="1">
+        <v>105.61</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
+        <v>126000</v>
+      </c>
+      <c r="N9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="6">
+        <v>277.01</v>
+      </c>
+      <c r="C14" s="6">
+        <v>5</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.5694</v>
+      </c>
+      <c r="E14" s="6">
+        <v>434.75</v>
+      </c>
+      <c r="F14" s="6">
+        <v>457.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="6">
-        <v>113.66</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.45</v>
-      </c>
-      <c r="E10" s="6">
-        <v>164.81</v>
-      </c>
-      <c r="F10" s="6">
-        <v>172.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="6">
-        <v>52.08</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.4032</v>
-      </c>
-      <c r="E11" s="6">
-        <v>73.08</v>
-      </c>
-      <c r="F11" s="6">
-        <v>77.95999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="9">
-        <v>165.74</v>
-      </c>
-      <c r="C12" s="9">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>237.89</v>
-      </c>
-      <c r="F12" s="9">
-        <v>250.73</v>
+      <c r="B15" s="6">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.4369</v>
+      </c>
+      <c r="E15" s="6">
+        <v>122.44</v>
+      </c>
+      <c r="F15" s="6">
+        <v>129.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="9">
+        <v>362.22</v>
+      </c>
+      <c r="C16" s="9">
+        <v>8</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9">
+        <v>557.1900000000001</v>
+      </c>
+      <c r="F16" s="9">
+        <v>586.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -193,7 +193,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1040,7 +1040,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="7">
-        <v>1.5694</v>
+        <v>1.569438</v>
       </c>
       <c r="E14" s="6">
         <v>434.75</v>
@@ -1060,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="7">
-        <v>1.4369</v>
+        <v>1.436921</v>
       </c>
       <c r="E15" s="6">
         <v>122.44</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -584,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -597,13 +600,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -646,362 +649,389 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2">
+        <v>64.283</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.406</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J2">
+        <v>92.95321800000001</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L2" s="1">
+        <v>97.71016</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2">
+        <v>123000</v>
+      </c>
+      <c r="O2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3">
+        <v>35.973</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>1.359</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J3">
+        <v>50.326227</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L3" s="1">
+        <v>53.9595</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="F2">
-        <v>64.28</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>49.382</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
+        <v>1.412</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J4">
+        <v>71.702664</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L4" s="1">
+        <v>75.06064000000001</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="H2">
-        <v>1.45</v>
-      </c>
-      <c r="I2" s="1">
-        <v>93.20999999999999</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
-        <v>97.70999999999999</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F5">
+        <v>16.107</v>
+      </c>
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="M2">
-        <v>123000</v>
-      </c>
-      <c r="N2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="H5">
+        <v>1.369</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="J5">
+        <v>22.694763</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L5" s="1">
+        <v>23.99943</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>46.351</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>1.528</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.568</v>
+      </c>
+      <c r="J6">
+        <v>72.67836800000001</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L6" s="1">
+        <v>77.86968</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E7" t="s">
         <v>33</v>
-      </c>
-      <c r="F3">
-        <v>35.97</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3">
-        <v>1.4</v>
-      </c>
-      <c r="I3" s="1">
-        <v>50.36</v>
-      </c>
-      <c r="J3">
-        <v>1.5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>53.96</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>49.38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4">
-        <v>1.45</v>
-      </c>
-      <c r="I4" s="1">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="J4">
-        <v>1.52</v>
-      </c>
-      <c r="K4" s="1">
-        <v>75.06</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5">
-        <v>16.11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5">
-        <v>1.41</v>
-      </c>
-      <c r="I5" s="1">
-        <v>22.72</v>
-      </c>
-      <c r="J5">
-        <v>1.49</v>
-      </c>
-      <c r="K5" s="1">
-        <v>24</v>
-      </c>
-      <c r="L5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>46.35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6">
-        <v>1.57</v>
-      </c>
-      <c r="I6" s="1">
-        <v>72.77</v>
-      </c>
-      <c r="J6">
-        <v>1.68</v>
-      </c>
-      <c r="K6" s="1">
-        <v>77.87</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
       </c>
       <c r="F7">
         <v>58</v>
       </c>
       <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
+        <v>1.619</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="J7">
+        <v>96.22199999999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L7" s="1">
+        <v>100.92</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7">
+        <v>126000</v>
+      </c>
+      <c r="O7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
         <v>34</v>
       </c>
-      <c r="H7">
-        <v>1.66</v>
-      </c>
-      <c r="I7" s="1">
-        <v>96.28</v>
-      </c>
-      <c r="J7">
-        <v>1.74</v>
-      </c>
-      <c r="K7" s="1">
-        <v>100.92</v>
-      </c>
-      <c r="L7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7">
-        <v>126000</v>
-      </c>
-      <c r="N7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="F8">
+        <v>33.129</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
+        <v>1.449</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.489</v>
+      </c>
+      <c r="J8">
+        <v>49.329081</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L8" s="1">
+        <v>51.34995</v>
+      </c>
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>33</v>
-      </c>
-      <c r="F8">
-        <v>33.13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8">
-        <v>1.49</v>
-      </c>
-      <c r="I8" s="1">
-        <v>49.36</v>
-      </c>
-      <c r="J8">
-        <v>1.55</v>
-      </c>
-      <c r="K8" s="1">
-        <v>51.35</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
       </c>
       <c r="F9">
         <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>1.71</v>
+        <v>1.674</v>
       </c>
       <c r="I9" s="1">
-        <v>100.89</v>
+        <v>1.714</v>
       </c>
       <c r="J9">
+        <v>101.126</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.79</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>105.61</v>
       </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9">
         <v>126000</v>
       </c>
-      <c r="N9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1009,79 +1039,79 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6">
-        <v>277.01</v>
+        <v>277.016</v>
       </c>
       <c r="C14" s="6">
         <v>5</v>
       </c>
       <c r="D14" s="7">
-        <v>1.569438</v>
+        <v>1.569159</v>
       </c>
       <c r="E14" s="6">
-        <v>434.75</v>
+        <v>434.68</v>
       </c>
       <c r="F14" s="6">
         <v>457.17</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6">
-        <v>85.20999999999999</v>
+        <v>85.209</v>
       </c>
       <c r="C15" s="6">
         <v>3</v>
       </c>
       <c r="D15" s="7">
-        <v>1.436921</v>
+        <v>1.435882</v>
       </c>
       <c r="E15" s="6">
-        <v>122.44</v>
+        <v>122.35</v>
       </c>
       <c r="F15" s="6">
         <v>129.31</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="9">
-        <v>362.22</v>
+        <v>362.225</v>
       </c>
       <c r="C16" s="9">
         <v>8</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9">
-        <v>557.1900000000001</v>
+        <v>557.03</v>
       </c>
       <c r="F16" s="9">
         <v>586.48</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ/ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -195,8 +192,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -289,10 +286,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -600,13 +597,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -649,389 +646,362 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>64.283</v>
       </c>
       <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2">
+        <v>1.446</v>
+      </c>
+      <c r="I2" s="1">
+        <v>92.953</v>
+      </c>
+      <c r="J2">
+        <v>1.52</v>
+      </c>
+      <c r="K2" s="1">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="H2">
-        <v>1.406</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.446</v>
-      </c>
-      <c r="J2">
-        <v>92.95321800000001</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L2" s="1">
-        <v>97.71016</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>123000</v>
       </c>
-      <c r="O2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>35.973</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>50.326</v>
       </c>
       <c r="J3">
-        <v>50.326227</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>53.9595</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3">
+        <v>53.96</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
         <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
       </c>
       <c r="F4">
         <v>49.382</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I4" s="1">
-        <v>1.452</v>
+        <v>71.703</v>
       </c>
       <c r="J4">
-        <v>71.702664</v>
+        <v>1.52</v>
       </c>
       <c r="K4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L4" s="1">
-        <v>75.06064000000001</v>
-      </c>
-      <c r="M4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4">
+        <v>75.06100000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>16.107</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>1.369</v>
+        <v>1.409</v>
       </c>
       <c r="I5" s="1">
-        <v>1.409</v>
+        <v>22.695</v>
       </c>
       <c r="J5">
-        <v>22.694763</v>
+        <v>1.49</v>
       </c>
       <c r="K5" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L5" s="1">
-        <v>23.99943</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5">
+        <v>23.999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
         <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
       </c>
       <c r="F6">
         <v>46.351</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>1.528</v>
+        <v>1.568</v>
       </c>
       <c r="I6" s="1">
-        <v>1.568</v>
+        <v>72.678</v>
       </c>
       <c r="J6">
-        <v>72.67836800000001</v>
+        <v>1.68</v>
       </c>
       <c r="K6" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L6" s="1">
-        <v>77.86968</v>
-      </c>
-      <c r="M6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6">
+        <v>77.87</v>
+      </c>
+      <c r="L6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>58</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>1.619</v>
+        <v>1.659</v>
       </c>
       <c r="I7" s="1">
-        <v>1.659</v>
+        <v>96.22199999999999</v>
       </c>
       <c r="J7">
-        <v>96.22199999999999</v>
+        <v>1.74</v>
       </c>
       <c r="K7" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L7" s="1">
         <v>100.92</v>
       </c>
-      <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
         <v>126000</v>
       </c>
-      <c r="O7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>33.129</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I8" s="1">
-        <v>1.489</v>
+        <v>49.329</v>
       </c>
       <c r="J8">
-        <v>49.329081</v>
+        <v>1.55</v>
       </c>
       <c r="K8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L8" s="1">
-        <v>51.34995</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8">
+        <v>51.35</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>1.674</v>
+        <v>1.714</v>
       </c>
       <c r="I9" s="1">
-        <v>1.714</v>
+        <v>101.126</v>
       </c>
       <c r="J9">
-        <v>101.126</v>
+        <v>1.79</v>
       </c>
       <c r="K9" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L9" s="1">
         <v>105.61</v>
       </c>
-      <c r="M9" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
         <v>126000</v>
       </c>
-      <c r="O9" t="s">
+      <c r="N9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1039,69 +1009,69 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="6">
         <v>277.016</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>5</v>
       </c>
       <c r="D14" s="7">
-        <v>1.569159</v>
-      </c>
-      <c r="E14" s="6">
-        <v>434.68</v>
-      </c>
-      <c r="F14" s="6">
-        <v>457.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>1.569</v>
+      </c>
+      <c r="E14" s="7">
+        <v>434.682</v>
+      </c>
+      <c r="F14" s="7">
+        <v>457.171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6">
         <v>85.209</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>3</v>
       </c>
       <c r="D15" s="7">
-        <v>1.435882</v>
-      </c>
-      <c r="E15" s="6">
+        <v>1.436</v>
+      </c>
+      <c r="E15" s="7">
         <v>122.35</v>
       </c>
-      <c r="F15" s="6">
-        <v>129.31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="F15" s="7">
+        <v>129.309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="9">
         <v>362.225</v>
@@ -1111,7 +1081,7 @@
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9">
-        <v>557.03</v>
+        <v>557.032</v>
       </c>
       <c r="F16" s="9">
         <v>586.48</v>
